--- a/questionnaire_templates/018_profile_questionnaire_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/018_profile_questionnaire_form--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>profile_questionnaire_form_page_1</t>
+          <t>profile_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Profile Information</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>profile_questionnaire_form_page_2</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marketing Information</t>
+          <t>What is your email address?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,58 +566,58 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_details</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Project Details</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>business_information</t>
+          <t>marketing_information</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Business Information</t>
+          <t>How would you like to be contacted?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>profiling_questionnaire</t>
+          <t>project_details</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Profiling Questionnaire</t>
+          <t>What is your project details?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>profile_questionnaire_form_page_6</t>
+          <t>business_information</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Business Information</t>
+          <t>What is your business information?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>What is your date of birth?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>What is your time of birth?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,64 +704,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>profile_questionnaire_form_page_9</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Any additional information?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>profile_questionnaire_form_page_10</t>
+          <t>profiling_questionnaire</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>What are your interests?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>profile_questionnaire_form_page_11</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>What is your age?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,41 +773,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>profile_questionnaire_form_page_12</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Profile Information</t>
+          <t>Where are you from?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>profile_questionnaire_form_page_13</t>
+          <t>education_level</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Marketing Information</t>
+          <t>What is your education level?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>business_information</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Business Information</t>
+          <t>What is your occupation?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,18 +842,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>project_details</t>
+          <t>interest</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Project Details</t>
+          <t>Why are you interested in this program?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,18 +865,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>project_details</t>
+          <t>project_details2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Project Details</t>
+          <t>What are the details about your project?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,202 +888,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>profiling_questionnaire_form_page_17</t>
+          <t>profile_questionnaire</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Profiling Information</t>
+          <t>Profiling Questionnaire</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>project_details</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Project Details</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>profile_questionnaire_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>profile_questionnaire_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>profile_questionnaire_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>profile_questionnaire_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>profile_questionnaire_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>profile_questionnaire_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Project Details</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>profile_questionnaire_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Profiling Information</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +965,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>profiling_questionnaire_choices</t>
+          <t>marketing_information_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'business'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'business'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>profiling_questionnaire_choices</t>
+          <t>marketing_information_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'marketing'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'marketing'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>marketing_information_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>profiling_questionnaire_choices</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'project'}</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'project'}</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>profiling_questionnaire_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>profiling_questionnaire_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hobbies</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hobbies</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>education_level_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>high_school</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>High School</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>education_level_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>College</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>education_level_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>education_level_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>phd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PhD</t>
         </is>
       </c>
     </row>
